--- a/Files/kalyan-penal-chart.xlsx
+++ b/Files/kalyan-penal-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$702</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$704</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -3155,6 +3155,12 @@
   </x:si>
   <x:si>
     <x:t>24/08/2026 to 29/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/09/2026 to 12/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026 to 19/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -3610,7 +3616,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V702"/>
+  <x:dimension ref="A1:V704"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -51299,49 +51305,49 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="F702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="G702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="H702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="I702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="L702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="M702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="N702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="O702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="P702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="Q702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S702" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="T702" s="3" t="s">
         <x:v>41</x:v>
@@ -51353,8 +51359,144 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="703" spans="1:22">
+      <x:c r="A703" s="3" t="s">
+        <x:v>1046</x:v>
+      </x:c>
+      <x:c r="B703" s="3" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C703" s="3" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D703" s="3" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="E703" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F703" s="3" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="G703" s="3" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="H703" s="3" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="I703" s="3" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="J703" s="3" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="K703" s="3" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L703" s="3" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="M703" s="3" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="N703" s="3" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="O703" s="3" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="P703" s="3" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="Q703" s="3" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="R703" s="3" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="S703" s="3" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="T703" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U703" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V703" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704" spans="1:22">
+      <x:c r="A704" s="3" t="s">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="B704" s="3" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="C704" s="3" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D704" s="3" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="E704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V704" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V702"/>
+  <x:autoFilter ref="A1:V704"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -51377,39 +51519,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>1046</x:v>
+        <x:v>1048</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>1047</x:v>
+        <x:v>1049</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>1048</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>1049</x:v>
+        <x:v>1051</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>1050</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>1051</x:v>
+        <x:v>1053</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>1052</x:v>
+        <x:v>1054</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>701</x:v>
+        <x:v>703</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>1053</x:v>
+        <x:v>1055</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -51417,10 +51559,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>1054</x:v>
+        <x:v>1056</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>1045</x:v>
+        <x:v>1047</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Files/kalyan-penal-chart.xlsx
+++ b/Files/kalyan-penal-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$704</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$705</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -3161,6 +3161,9 @@
   </x:si>
   <x:si>
     <x:t>14/09/2026 to 19/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026 to 26/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -3616,7 +3619,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V704"/>
+  <x:dimension ref="A1:V705"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -51441,49 +51444,49 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="E704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="I704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="K704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="L704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="M704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="N704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="O704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="P704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="Q704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="R704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="S704" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="T704" s="3" t="s">
         <x:v>41</x:v>
@@ -51495,8 +51498,76 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="705" spans="1:22">
+      <x:c r="A705" s="3" t="s">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="B705" s="3" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C705" s="3" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D705" s="3" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E705" s="3" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="F705" s="3" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G705" s="3" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="H705" s="3" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="I705" s="3" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J705" s="3" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="K705" s="3" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="L705" s="3" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="M705" s="3" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="N705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V705" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V704"/>
+  <x:autoFilter ref="A1:V705"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -51519,39 +51590,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>1048</x:v>
+        <x:v>1049</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>1049</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>1050</x:v>
+        <x:v>1051</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>1051</x:v>
+        <x:v>1052</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>1052</x:v>
+        <x:v>1053</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>1053</x:v>
+        <x:v>1054</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>1054</x:v>
+        <x:v>1055</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>703</x:v>
+        <x:v>704</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>1055</x:v>
+        <x:v>1056</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -51559,10 +51630,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>1056</x:v>
+        <x:v>1057</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>1047</x:v>
+        <x:v>1048</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
